--- a/docs/PRAP_Development_Plan_v2.60.xlsx
+++ b/docs/PRAP_Development_Plan_v2.60.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Version_History" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Scope" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Requirements" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Data_Model" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Resource_Logic" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Dashboard_Design" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Architecture" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_WBS_Schedule" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Version_Control" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Risks" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Open_Questions" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Review_Log" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="00_Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_Version_History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_Scope" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_Requirements" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_Data_Model" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_Resource_Logic" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06_Dashboard_Design" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="07_Architecture" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="08_WBS_Schedule" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="09_Version_Control" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10_Risks" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11_Open_Questions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12_Review_Log" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20371,7 +20371,7 @@
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>PRAP_SourceData_Template_v1.6.xlsx</t>
+          <t>PRAP_SourceData_Template_v1.16.xlsx</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
